--- a/bulk_upload_module/templates/sample_drive_results.xlsx
+++ b/bulk_upload_module/templates/sample_drive_results.xlsx
@@ -644,6 +644,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid result status." type="list">
+      <formula1>"Shortlisted for Round 2,Shortlisted for Round 3,Selected,Rejected,On Hold,Absent"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>